--- a/41-ajouter-la-modélisation-des-ressources/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/41-ajouter-la-modélisation-des-ressources/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T14:31:58+00:00</t>
+    <t>2024-07-08T16:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/41-ajouter-la-modélisation-des-ressources/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/41-ajouter-la-modélisation-des-ressources/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T16:25:19+00:00</t>
+    <t>2024-07-08T17:03:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/41-ajouter-la-modélisation-des-ressources/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/41-ajouter-la-modélisation-des-ressources/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T17:03:42+00:00</t>
+    <t>2024-07-09T09:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/41-ajouter-la-modélisation-des-ressources/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/41-ajouter-la-modélisation-des-ressources/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T09:03:55+00:00</t>
+    <t>2024-07-09T09:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
